--- a/per-stock/IREN/financials.xlsx
+++ b/per-stock/IREN/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18919626752</v>
+        <v>21428426752</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20671266816</v>
+        <v>23180064768</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68.75324999999999</v>
+        <v>77.87013</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-39.36059</v>
+        <v>-63.78723</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.99046</v>
+        <v>28.30427</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-2311044352</v>
+        <v>-2448133000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52.94</v>
+        <v>59.96</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D61</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C61</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B61</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B56:E56)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D59</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C59</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B59</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B54:E54)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D45</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C45</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B45</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B41:E41)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2044,13 +2524,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2540,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2070,30 +2551,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -2106,21 +2592,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-4194425</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-77513700</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>211040635</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>21096900</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>1259182.013872</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>-11108400</v>
+        <v>-11036100</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2129,21 +2616,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.331</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.3</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.172208</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2152,21 +2640,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>49773000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>30296000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>32219000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>82806000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>77271000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>55944000</v>
+        <v>77111000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2175,21 +2664,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-167777000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-258379000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>637585000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>70323000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>7312000</v>
-      </c>
       <c r="F5" s="3" t="n">
-        <v>-37028000</v>
+        <v>-36787000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2198,21 +2688,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-167777000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-258379000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>637585000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>70323000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>7312000</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>-37028000</v>
+        <v>-36787000</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2221,21 +2712,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-247827000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-155407000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>384611000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>95546000</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>24227000</v>
-      </c>
       <c r="F7" s="3" t="n">
-        <v>-21888000</v>
+        <v>-16144000</v>
       </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2244,21 +2736,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>121245000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>99176000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>85226000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>63481000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>47448000</v>
-      </c>
       <c r="F8" s="3" t="n">
-        <v>36077000</v>
+        <v>47311000</v>
       </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2267,21 +2760,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>51225000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>74316000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>89037000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>136822000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>7464000</v>
-      </c>
       <c r="F9" s="3" t="n">
-        <v>37196000</v>
+        <v>46906000</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2290,21 +2784,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-118004000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-228083000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>669804000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>153129000</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>84583000</v>
-      </c>
       <c r="F10" s="3" t="n">
-        <v>18916000</v>
+        <v>40324000</v>
       </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2313,21 +2808,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-239249000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-327259000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>584578000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>89648000</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>37135000</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>-17161000</v>
+        <v>-6987000</v>
       </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2336,21 +2832,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>6962000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>5107000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-2152000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>4843000</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>-5942000</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>-135000</v>
+        <v>-2194000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2359,21 +2856,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>14837000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>10668000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>9280000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-3140000</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>7868000</v>
-      </c>
       <c r="F13" s="3" t="n">
-        <v>1722000</v>
+        <v>4119000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2382,21 +2880,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>21799000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>15775000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>7128000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>1703000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1926000</v>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>1587000</v>
+        <v>1925000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2405,21 +2904,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-84244425</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>25458300</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-41933365</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>46319900</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>18174182.013872</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>4031600</v>
+        <v>9606900</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2428,21 +2928,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-247827000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-155407000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>384611000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>95546000</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>24227000</v>
-      </c>
       <c r="F16" s="3" t="n">
-        <v>-21888000</v>
+        <v>-16144000</v>
       </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2451,21 +2952,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>238141000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>269347000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>300430000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>170487000</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>116926000</v>
-      </c>
       <c r="F17" s="3" t="n">
-        <v>98154000</v>
+        <v>117134000</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2473,22 +2975,23 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n">
         <v>-116403000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-76405000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>4549000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>35527000</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="G18" s="3" t="n">
         <v>17310000</v>
       </c>
-      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2497,21 +3000,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>333734176</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>331759177</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>361680593</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>258103209</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>229105785</v>
-      </c>
       <c r="F19" s="3" t="n">
-        <v>210470186</v>
+        <v>218659835</v>
       </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2520,21 +3024,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>333734176</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>331759177</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>270696733</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>258103209</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>218659835</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>210470186</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2543,21 +3048,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-0.52</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.685385</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>0.11</v>
-      </c>
       <c r="F21" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2566,21 +3072,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-0.52</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1.42</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.685385</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>0.11</v>
-      </c>
       <c r="F22" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2589,21 +3096,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-247827000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-155407000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>384611000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>95546000</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>24227000</v>
-      </c>
       <c r="F23" s="3" t="n">
-        <v>-21888000</v>
+        <v>-16144000</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2612,21 +3120,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-247827000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-155407000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>384611000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>95546000</v>
       </c>
-      <c r="E24" s="3" t="n">
-        <v>24227000</v>
-      </c>
       <c r="F24" s="3" t="n">
-        <v>-21888000</v>
+        <v>-16144000</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2635,21 +3144,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-247827000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-155407000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>384611000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>95546000</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>24227000</v>
-      </c>
       <c r="F25" s="3" t="n">
-        <v>-21888000</v>
+        <v>-16144000</v>
       </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2658,21 +3168,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-247827000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-155407000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>384611000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>95546000</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>24227000</v>
-      </c>
       <c r="F26" s="3" t="n">
-        <v>-21888000</v>
+        <v>-16144000</v>
       </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2681,21 +3192,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-247827000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-155407000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>384611000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>95546000</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>24227000</v>
-      </c>
       <c r="F27" s="3" t="n">
-        <v>-21888000</v>
+        <v>-16144000</v>
       </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2704,21 +3216,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-6259000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-182520000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>190687000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-2758000</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>5040000</v>
-      </c>
       <c r="F28" s="3" t="n">
-        <v>3005000</v>
+        <v>5038000</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2727,21 +3240,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-254086000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-337927000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>575298000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>92788000</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>29267000</v>
-      </c>
       <c r="F29" s="3" t="n">
-        <v>-18883000</v>
+        <v>-11106000</v>
       </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2750,21 +3264,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-167702000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-258379000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>637585000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>71140000</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>7312000</v>
-      </c>
       <c r="F30" s="3" t="n">
-        <v>-36739000</v>
+        <v>-36601000</v>
       </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2772,16 +3287,19 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
+      <c r="B31" s="3" t="n">
+        <v>75000</v>
+      </c>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n">
-        <v>3275000</v>
-      </c>
+      <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
+        <v>186000</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>289000</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="H31" s="3" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -2792,21 +3310,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-140177000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-143547000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-16270000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>11723000</v>
       </c>
-      <c r="E32" s="3" t="n">
-        <v>1430000</v>
-      </c>
       <c r="F32" s="3" t="n">
-        <v>-681000</v>
+        <v>1526000</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2815,21 +3334,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>234000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>7000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-13000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>2324000</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>1525000</v>
-      </c>
       <c r="F33" s="3" t="n">
-        <v>-681000</v>
+        <v>1526000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2837,16 +3357,17 @@
           <t>Other Special Charges</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
         <v>111799000</v>
       </c>
-      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
         <v>-1699000</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>1724000</v>
       </c>
     </row>
@@ -2857,21 +3378,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>140411000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>31755000</v>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n">
         <v>-8070000</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>95000</v>
-      </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>9524000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2880,19 +3402,20 @@
         </is>
       </c>
       <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
         <v>16257000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>7739000</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>-516000</v>
       </c>
-      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2901,21 +3424,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-27600000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-114832000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>653855000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>58600000</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>5882000</v>
-      </c>
       <c r="F37" s="3" t="n">
-        <v>-36347000</v>
+        <v>-38313000</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2924,21 +3448,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>6962000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>5107000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-2152000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>4843000</v>
       </c>
-      <c r="E38" s="3" t="n">
-        <v>-5942000</v>
-      </c>
       <c r="F38" s="3" t="n">
-        <v>-135000</v>
+        <v>-2194000</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2947,21 +3472,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>14837000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>10668000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>9280000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-3140000</v>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>7868000</v>
-      </c>
       <c r="F39" s="3" t="n">
-        <v>1722000</v>
+        <v>4119000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2970,21 +3496,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>21799000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>15775000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>7128000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1703000</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>1926000</v>
-      </c>
       <c r="F40" s="3" t="n">
-        <v>1587000</v>
+        <v>1925000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2993,21 +3520,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-93346000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-84655000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-60135000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>16805000</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>27897000</v>
-      </c>
       <c r="F41" s="3" t="n">
-        <v>17990000</v>
+        <v>27689000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3016,21 +3544,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>186916000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>195031000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>211393000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>33665000</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>109462000</v>
-      </c>
       <c r="F42" s="3" t="n">
-        <v>60958000</v>
+        <v>70228000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3039,21 +3568,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-4787000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>3653000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-3828000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-132313000</v>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>50557000</v>
-      </c>
       <c r="F43" s="3" t="n">
-        <v>890000</v>
+        <v>-1225000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3062,19 +3592,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>3844000</v>
+        <v>9914000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>3124000</v>
-      </c>
-      <c r="D44" s="3" t="n"/>
+        <v>10687000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>35898000</v>
+      </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
-        <v>1560000</v>
+        <v>2332000</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1298000</v>
-      </c>
+        <v>2031000</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3083,21 +3616,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>121245000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>99176000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>85226000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>63481000</v>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>47448000</v>
-      </c>
       <c r="F45" s="3" t="n">
-        <v>36077000</v>
+        <v>47311000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3106,21 +3640,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>121245000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>99176000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>85226000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>63481000</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>47448000</v>
-      </c>
       <c r="F46" s="3" t="n">
-        <v>36077000</v>
+        <v>47311000</v>
       </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3131,13 +3666,14 @@
       <c r="B47" s="3" t="n"/>
       <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n">
         <v>47448000</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="G47" s="3" t="n">
         <v>36198000</v>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="H47" s="3" t="n">
         <v>34009000</v>
       </c>
     </row>
@@ -3148,21 +3684,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>88358000</v>
+        <v>60544000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>126871000</v>
+        <v>81515000</v>
       </c>
       <c r="D48" s="3" t="n">
+        <v>94097000</v>
+      </c>
+      <c r="E48" s="3" t="n">
         <v>93254000</v>
       </c>
-      <c r="E48" s="3" t="n">
-        <v>11457000</v>
-      </c>
       <c r="F48" s="3" t="n">
-        <v>22431000</v>
+        <v>21810000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3171,19 +3708,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>8843000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>1997000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>3080000</v>
       </c>
-      <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
+        <v>619000</v>
+      </c>
+      <c r="G49" s="3" t="n">
         <v>857000</v>
       </c>
-      <c r="G49" s="3" t="n">
-        <v>578000</v>
-      </c>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3192,21 +3732,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>86361000</v>
+        <v>51701000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>123791000</v>
+        <v>79518000</v>
       </c>
       <c r="D50" s="3" t="n">
+        <v>91017000</v>
+      </c>
+      <c r="E50" s="3" t="n">
         <v>90370000</v>
       </c>
-      <c r="E50" s="3" t="n">
-        <v>11457000</v>
-      </c>
       <c r="F50" s="3" t="n">
-        <v>21574000</v>
+        <v>21191000</v>
       </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3215,21 +3756,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>14517000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>17464000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>13439000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>26022000</v>
       </c>
-      <c r="E51" s="3" t="n">
-        <v>3687000</v>
-      </c>
       <c r="F51" s="3" t="n">
-        <v>8478000</v>
+        <v>8494000</v>
       </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3238,19 +3780,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>5697000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>3823000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>5173000</v>
       </c>
-      <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n">
+        <v>4927000</v>
+      </c>
+      <c r="G52" s="3" t="n">
         <v>4650000</v>
       </c>
-      <c r="G52" s="3" t="n">
-        <v>2992000</v>
-      </c>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3259,21 +3804,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>65074000</v>
+        <v>31487000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>105179000</v>
+        <v>58231000</v>
       </c>
       <c r="D53" s="3" t="n">
+        <v>72405000</v>
+      </c>
+      <c r="E53" s="3" t="n">
         <v>46246000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>7770000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>8446000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3282,21 +3828,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>93570000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>110376000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>151258000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>50470000</v>
       </c>
-      <c r="E54" s="3" t="n">
-        <v>137359000</v>
-      </c>
       <c r="F54" s="3" t="n">
-        <v>78948000</v>
+        <v>97917000</v>
       </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3305,21 +3852,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>51225000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>74316000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>89037000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>136822000</v>
       </c>
-      <c r="E55" s="3" t="n">
-        <v>7464000</v>
-      </c>
       <c r="F55" s="3" t="n">
-        <v>37196000</v>
+        <v>46906000</v>
       </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3328,21 +3876,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>144795000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>184692000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>240295000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>187292000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>144823000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>116144000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3351,28 +3900,29 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>144795000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>184692000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>240295000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>187292000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>144823000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>116144000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5066,7 +5616,2007 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>340979966</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>331759177</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>282876303</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>258103209</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>224458888</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>340979966</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>331759177</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>282876303</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>258103209</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>224458888</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1474558000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>424707000</v>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n">
+        <v>398239000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>138147000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3964913000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3842548000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>965632000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>964232000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>324075000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2555725000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2403620000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2876167000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1817488000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1425567000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6352360000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6196489000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3840376000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2780253000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1748047000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1773130000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2701290000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>920195000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>491826000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-297196000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2555725000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2403620000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2876167000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1817488000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1425567000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>277081000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>157252000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1423000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1467000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1595000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2664528000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2511193000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2876167000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1817488000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1425567000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>6352360000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>6196489000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3840376000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2780253000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1425567000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2664528000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2511193000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2876167000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1817488000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1425567000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2664528000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2511193000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2876167000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1817488000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1425567000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>69969000</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>62339000</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>54446000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-39398000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-32290000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-35531000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-30073000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-45074000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-39398000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-32290000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-35531000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-30073000</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Foreign Currency Translation Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n">
+        <v>-45074000</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-45116000</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-33143000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-614790000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-366963000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-211556000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-596167000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-691836000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-1728367000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-1757926000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>157666000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>88672000</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>5047083000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>4668372000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2965588000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2355056000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2092508000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>5047083000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>4668372000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2965588000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2355056000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2092508000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>4600369000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>4516384000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1391207000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1122835000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>564188000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3949013000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3834253000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1187462000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>973488000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>11081000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n">
+        <v>235000</v>
+      </c>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>339000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>306000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>289000</v>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
+        <v>204000</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>192000</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>7230000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>5769000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>4296000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1454000</v>
+      </c>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>99238000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>47886000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>217645000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>7971000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>9645000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>98598000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>39831000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>22234000</v>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>640000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>8055000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>195411000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>7971000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>9645000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3842205000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3780292000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>965232000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>963828000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1232000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>154373000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>94996000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1023000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1063000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1232000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>3687832000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>3685296000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>964209000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>962765000</v>
+      </c>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>651356000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>682131000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>203745000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>149347000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>553107000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>5804000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1905000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2376000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>3944000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>23700000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>21790000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>6794000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1107000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>884000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1671000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>21790000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>6794000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1107000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>884000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1671000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>122708000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>62256000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>404000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>322843000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>122708000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>62256000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>404000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>363000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n">
+        <v>322480000</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>318214000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n">
+        <v>322480000</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>318214000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>14330000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>9146000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>7140000</v>
+      </c>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n">
+        <v>6771000</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>5039000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>486724000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>602030000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>192722000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>144115000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>198122000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>373920000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>346220000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>91251000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>42368000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>4574000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>9133000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2542000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>10315000</v>
+      </c>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n">
+        <v>4574000</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>999000</v>
+      </c>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>112804000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>255810000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>101471000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>101747000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>193548000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>15755000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>23220000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>30533000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>21276000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>910000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>752000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>134000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1585000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>97049000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>232590000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>70938000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>81747000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>172272000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>7264897000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>7027577000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>4267374000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2940323000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1989755000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>4840411000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>3644156000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3143434000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>2299150000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1733844000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>4993000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>282000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>317000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>486000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>466000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>161805000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>148822000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>30456000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>29847000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>24354000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>215700000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>995800000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>333717000</v>
+      </c>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>34717000</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>56017000</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>34717000</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>56017000</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Financial Assets Designatedas Fair Value Through Profitor Loss Total</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n">
+        <v>34717000</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>56017000</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>108803000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>107573000</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>107623000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>107573000</v>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>1180000</v>
+      </c>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>4372810000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>3171779000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2116861000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1935100000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1674307000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>-617119000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>-383282000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>-281423000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-181631000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>-124373000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>4989929000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>3555061000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>2398284000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>2116731000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1798680000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>37000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>43000</v>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>2089371000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1038321000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>464832000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>240802000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>311335000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>304724000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>161370000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1463000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1628000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1861984000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1638683000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1247564000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>1221587000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>955898000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>690060000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>686948000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>671382000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>639750000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>517770000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>43756000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>29702000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>13043000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>13086000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>12049000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>2424486000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>3383421000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1123940000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>641173000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>255911000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>2910000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>5756000</v>
+      </c>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>6491000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>20102000</v>
+      </c>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n">
+        <v>1310000</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>2952000</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>10696000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>89958000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>55330000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>53275000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>45909000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>37555000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>114762000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>47400000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>35492000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>24983000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>21013000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>45675000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>37794000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>11353000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>5342000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>3843000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>17440000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>16883000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Accrued Interest Receivable</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n"/>
+      <c r="C80" s="3" t="n"/>
+      <c r="D80" s="3" t="n"/>
+      <c r="E80" s="3" t="n">
+        <v>637000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>285000</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>738000</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>158000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>69087000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>9606000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>24139000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>1564000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>2213274000</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>3260589000</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1032263000</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>564526000</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>196033000</v>
+      </c>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n"/>
+      <c r="C83" s="3" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>11700000</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>28300000</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>2213274000</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>3260589000</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1032263000</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>564526000</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>184333000</v>
+      </c>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n"/>
+      <c r="C85" s="3" t="n"/>
+      <c r="D85" s="3" t="n"/>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n"/>
+      <c r="C86" s="3" t="n"/>
+      <c r="D86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n">
+        <v>184333000</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>427273000</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>98589000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6414,13 +8964,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6430,6 +8980,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6440,30 +8991,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -6476,21 +9032,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-1279903000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-765204000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-138258000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>49220000</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-654651000</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>-134006000</v>
+        <v>-350700000</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6498,18 +9055,21 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="n">
+        <v>-17612000</v>
+      </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n">
         <v>349000</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>-349000</v>
-      </c>
       <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>-124000</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>-99000</v>
       </c>
     </row>
@@ -6519,16 +9079,19 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n">
         <v>389565000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n"/>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6537,21 +9100,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>380032000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1632528000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>618912000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>262551000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>107606000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>147753000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6560,1205 +9124,1434 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-1355225000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-836855000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-280611000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-357872000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-443804000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-187562000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>End Cash Position</t>
+          <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3260589000</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1032263000</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>564526000</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>184333000</v>
-      </c>
+        <v>4280000</v>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
-        <v>427273000</v>
+        <v>22000</v>
       </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beginning Cash Position</t>
+          <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1032263000</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>564526000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>184333000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>427273000</v>
-      </c>
+        <v>87000</v>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n">
-        <v>98589000</v>
+        <v>1004000</v>
       </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Effect Of Exchange Rate Changes</t>
+          <t>End Cash Position</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>28000</v>
+        <v>2213274000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>124000</v>
+        <v>3260589000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1304000</v>
+        <v>1032263000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-289000</v>
+        <v>564526000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-1595000</v>
+        <v>184333000</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Changes In Cash</t>
+          <t>Beginning Cash Position</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2228298000</v>
+        <v>3260589000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>467613000</v>
+        <v>1032263000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>378889000</v>
+        <v>564526000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-242651000</v>
+        <v>184333000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>330279000</v>
+        <v>427273000</v>
       </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Financing Cash Flow</t>
+          <t>Effect Of Exchange Rate Changes</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3007598000</v>
+        <v>-568000</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>606137000</v>
+        <v>28000</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>646273000</v>
+        <v>124000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>106777000</v>
+        <v>1304000</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>457016000</v>
+        <v>-289000</v>
       </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Financing Activities</t>
+          <t>Changes In Cash</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3007598000</v>
+        <v>-1046747000</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>606137000</v>
+        <v>2228298000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>646273000</v>
+        <v>467613000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>106777000</v>
+        <v>378889000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>457016000</v>
+        <v>-242651000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Net Other Financing Charges</t>
+          <t>Financing Cash Flow</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-301001000</v>
+        <v>355034000</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-19372000</v>
+        <v>3007598000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-6192000</v>
+        <v>606137000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-480000</v>
+        <v>646273000</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-2383000</v>
+        <v>107126000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Proceeds From Stock Option Exercised</t>
+          <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0</v>
+        <v>355034000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6597000</v>
-      </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+        <v>3007598000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>606137000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>646273000</v>
+      </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>107126000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
+          <t>Net Other Financing Charges</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1632528000</v>
+        <v>-7386000</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>618912000</v>
+        <v>-301001000</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>262551000</v>
+        <v>-19372000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>107606000</v>
+        <v>-6192000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>147753000</v>
+        <v>-480000</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Common Stock Issuance</t>
+          <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1632528000</v>
+        <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>618912000</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>262551000</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>107606000</v>
-      </c>
+        <v>6597000</v>
+      </c>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n">
-        <v>147753000</v>
-      </c>
-      <c r="G16" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+          <t>Net Common Stock Issuance</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>380032000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1632528000</v>
+      </c>
       <c r="D17" s="3" t="n">
-        <v>389914000</v>
+        <v>618912000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-349000</v>
+        <v>262551000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>311522000</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>-99000</v>
-      </c>
+        <v>107606000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Net Short Term Debt Issuance</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+          <t>Common Stock Issuance</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>380032000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1632528000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>618912000</v>
+      </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n"/>
+        <v>262551000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>107606000</v>
+      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Short Term Debt Issuance</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
+          <t>Net Issuance Payments Of Debt</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-17612000</v>
+      </c>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
+        <v>389914000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>311522000</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>-99000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Net Short Term Debt Issuance</t>
         </is>
       </c>
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>389914000</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-349000</v>
-      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n">
-        <v>311522000</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>-99000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Short Term Debt Issuance</t>
         </is>
       </c>
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n">
-        <v>349000</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-349000</v>
-      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n">
-        <v>-124000</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-99000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Long Term Debt Issuance</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
+          <t>Net Long Term Debt Issuance</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-17612000</v>
+      </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
-        <v>389565000</v>
-      </c>
+      <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+        <v>389914000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>311522000</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>-99000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-850951000</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>-280877000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>-674476000</v>
-      </c>
+        <v>-17612000</v>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n">
-        <v>-138581000</v>
+        <v>349000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-180293000</v>
-      </c>
-      <c r="G23" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-124000</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-99000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-850951000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-280877000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>-674476000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n">
-        <v>-138581000</v>
+        <v>389565000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-180293000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Net Other Investing Changes</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-14096000</v>
+        <v>-1477103000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-266000</v>
+        <v>-850951000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-13506000</v>
+        <v>-280877000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-1199000</v>
+        <v>-674476000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-540000</v>
+        <v>-442881000</v>
       </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
+          <t>Cash Flow From Continuing Investing Activities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-1477103000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-850951000</v>
+      </c>
       <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n">
-        <v>49575000</v>
-      </c>
+        <v>-280877000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-674476000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-442881000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
+          <t>Net Other Investing Changes</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-144697000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-14096000</v>
+      </c>
       <c r="D27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n">
-        <v>49575000</v>
-      </c>
+        <v>-266000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-13506000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-1199000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Intangibles Purchase And Sale</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n">
-        <v>304300000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>113483000</v>
-      </c>
-      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n">
         <v>49575000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sale Of Intangibles</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n">
-        <v>141242000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>113483000</v>
-      </c>
-      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n">
         <v>49575000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Net Intangibles Purchase And Sale</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-729282000</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>-280611000</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>-356670000</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-442152000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n">
-        <v>-179753000</v>
-      </c>
-      <c r="G30" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>113483000</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>49575000</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sale Of PPE</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>1202000</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>1652000</v>
-      </c>
+          <t>Sale Of Intangibles</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>7809000</v>
-      </c>
-      <c r="G31" s="3" t="n"/>
+        <v>141242000</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>113483000</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>49575000</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
+          <t>Purchase Of Intangibles</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-729282000</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>-280611000</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>-357872000</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-443804000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n">
-        <v>-187562000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>71651000</v>
+        <v>-1332406000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>142353000</v>
-      </c>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
+        <v>-729282000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-280611000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-356670000</v>
+      </c>
       <c r="F33" s="3" t="n">
-        <v>53556000</v>
+        <v>-442152000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Sale Of PPE</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>71651000</v>
+        <v>22819000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>142353000</v>
-      </c>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1202000</v>
+      </c>
       <c r="F34" s="3" t="n">
-        <v>53556000</v>
+        <v>1652000</v>
       </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-198160000</v>
+        <v>-1355225000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>239537000</v>
-      </c>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
+        <v>-729282000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-280611000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-357872000</v>
+      </c>
       <c r="F35" s="3" t="n">
-        <v>-5787000</v>
+        <v>-443804000</v>
       </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>23284000</v>
+        <v>75322000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>22457000</v>
-      </c>
-      <c r="D36" s="3" t="n"/>
+        <v>71651000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>142353000</v>
+      </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n">
-        <v>-59000</v>
-      </c>
-      <c r="G36" s="3" t="n"/>
+        <v>93104000</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>53556000</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Change In Other Current Liabilities</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-13099000</v>
+        <v>75322000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>48635000</v>
-      </c>
-      <c r="D37" s="3" t="n"/>
+        <v>71651000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>142353000</v>
+      </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n">
-        <v>1686000</v>
-      </c>
-      <c r="G37" s="3" t="n"/>
+        <v>93104000</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>53556000</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Change In Other Current Assets</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>35000</v>
+        <v>2513000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>169000</v>
-      </c>
-      <c r="D38" s="3" t="n"/>
+        <v>-198160000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>239537000</v>
+      </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n">
-        <v>-35000</v>
-      </c>
-      <c r="G38" s="3" t="n"/>
+        <v>12594000</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-5787000</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-192802000</v>
+        <v>73763000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>191432000</v>
-      </c>
-      <c r="D39" s="3" t="n"/>
+        <v>23284000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>22457000</v>
+      </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
-        <v>784000</v>
-      </c>
-      <c r="G39" s="3" t="n"/>
+        <v>-619000</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>-59000</v>
+      </c>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Other Current Liabilities</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-192802000</v>
+        <v>10662000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>191432000</v>
-      </c>
-      <c r="D40" s="3" t="n"/>
+        <v>-13099000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>48635000</v>
+      </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n">
-        <v>784000</v>
-      </c>
-      <c r="G40" s="3" t="n"/>
+        <v>5384000</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1686000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Other Current Assets</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-12505000</v>
+        <v>-4711000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>3489000</v>
-      </c>
-      <c r="D41" s="3" t="n"/>
+        <v>35000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>169000</v>
+      </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n">
-        <v>-582000</v>
-      </c>
-      <c r="G41" s="3" t="n"/>
+        <v>150000</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Change In Tax Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-180297000</v>
+        <v>8450000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>187943000</v>
-      </c>
-      <c r="D42" s="3" t="n"/>
+        <v>-192802000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>191432000</v>
+      </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n">
-        <v>1366000</v>
-      </c>
-      <c r="G42" s="3" t="n"/>
+        <v>-30190000</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>784000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Change In Income Tax Payable</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-180297000</v>
+        <v>8450000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>187943000</v>
-      </c>
-      <c r="D43" s="3" t="n"/>
+        <v>-192802000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>191432000</v>
+      </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n">
-        <v>1366000</v>
-      </c>
-      <c r="G43" s="3" t="n"/>
+        <v>-30190000</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>784000</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Change In Prepaid Assets</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>-1089000</v>
+        <v>15877000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>-12647000</v>
-      </c>
-      <c r="D44" s="3" t="n"/>
+        <v>-12505000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3489000</v>
+      </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
-        <v>-22184000</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
+        <v>-34218000</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>-582000</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Tax Payable</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>-14489000</v>
+        <v>-7427000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>-10509000</v>
-      </c>
-      <c r="D45" s="3" t="n"/>
+        <v>-180297000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>187943000</v>
+      </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n">
-        <v>14021000</v>
-      </c>
-      <c r="G45" s="3" t="n"/>
+        <v>4028000</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>1366000</v>
+      </c>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Income Tax Payable</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-11908000</v>
+        <v>-7427000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-13090000</v>
-      </c>
-      <c r="D46" s="3" t="n"/>
+        <v>-180297000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>187943000</v>
+      </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>14021000</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
+        <v>4028000</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1366000</v>
+      </c>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Change In Prepaid Assets</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>113840000</v>
+        <v>-18288000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1340000</v>
-      </c>
-      <c r="D47" s="3" t="n"/>
+        <v>-1089000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>-12647000</v>
+      </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n">
-        <v>-2431000</v>
-      </c>
-      <c r="G47" s="3" t="n"/>
+        <v>48985000</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>-22184000</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>58231000</v>
+        <v>-67363000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>72405000</v>
-      </c>
-      <c r="D48" s="3" t="n"/>
+        <v>-14489000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-10509000</v>
+      </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n">
-        <v>7975000</v>
-      </c>
-      <c r="G48" s="3" t="n"/>
+        <v>-11116000</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>14021000</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unrealized Gain Loss On Investment Securities</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>107351000</v>
+        <v>-67363000</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>-664993000</v>
-      </c>
-      <c r="D49" s="3" t="n"/>
+        <v>-11908000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>-13090000</v>
+      </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
-        <v>32300000</v>
-      </c>
-      <c r="G49" s="3" t="n"/>
+        <v>-11116000</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>14021000</v>
+      </c>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Asset Impairment Charge</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>38204000</v>
+        <v>4779000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>16257000</v>
-      </c>
-      <c r="D50" s="3" t="n"/>
+        <v>120289000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1340000</v>
+      </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n">
-        <v>2066000</v>
-      </c>
-      <c r="G50" s="3" t="n"/>
+        <v>2098000</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-365000</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>99176000</v>
+        <v>31487000</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>85226000</v>
-      </c>
-      <c r="D51" s="3" t="n"/>
+        <v>58231000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>72405000</v>
+      </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n">
-        <v>36077000</v>
-      </c>
-      <c r="G51" s="3" t="n"/>
+        <v>7770000</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>7975000</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Unrealized Gain Loss On Investment Securities</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>99176000</v>
+        <v>23700000</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>85226000</v>
-      </c>
-      <c r="D52" s="3" t="n"/>
+        <v>107351000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-664993000</v>
+      </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n">
-        <v>36077000</v>
-      </c>
-      <c r="G52" s="3" t="n"/>
+        <v>37900000</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>32300000</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Asset Impairment Charge</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>8416000</v>
+        <v>140411000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>7970000</v>
-      </c>
-      <c r="D53" s="3" t="n"/>
+        <v>31755000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>16257000</v>
+      </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n">
-        <v>5244000</v>
-      </c>
-      <c r="G53" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gain Loss On Investment Securities</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2910000</v>
+        <v>121245000</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>5756000</v>
-      </c>
-      <c r="D54" s="3" t="n"/>
+        <v>99176000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>85226000</v>
+      </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3" t="n"/>
+        <v>47311000</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>36077000</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Net Foreign Currency Exchange Gain Loss</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>5513000</v>
+        <v>121245000</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2201000</v>
-      </c>
-      <c r="D55" s="3" t="n"/>
+        <v>99176000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>85226000</v>
+      </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n">
-        <v>4563000</v>
-      </c>
-      <c r="G55" s="3" t="n"/>
+        <v>47311000</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>36077000</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gain Loss On Sale Of PPE</t>
+          <t>Operating Gains Losses</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>-7000</v>
+        <v>-987000</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>13000</v>
-      </c>
-      <c r="D56" s="3" t="n"/>
+        <v>8416000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>7970000</v>
+      </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n">
-        <v>681000</v>
-      </c>
-      <c r="G56" s="3" t="n"/>
+        <v>1575000</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>5244000</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Net Income From Continuing Operations</t>
+          <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>-155407000</v>
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>384611000</v>
-      </c>
-      <c r="D57" s="3" t="n"/>
+        <v>2910000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>5756000</v>
+      </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n">
-        <v>-21888000</v>
-      </c>
-      <c r="G57" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cash Flowsfromusedin Operating Activities Direct</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n">
-        <v>-48012000</v>
-      </c>
+          <t>Net Foreign Currency Exchange Gain Loss</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>-753000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>5513000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2201000</v>
+      </c>
+      <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n">
-        <v>-59803000</v>
+        <v>3101000</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-53391000</v>
-      </c>
+        <v>4563000</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Interest Received Direct</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n">
-        <v>2381000</v>
-      </c>
+          <t>Gain Loss On Sale Of PPE</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-234000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n">
-        <v>992000</v>
+        <v>-1526000</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3637000</v>
-      </c>
+        <v>681000</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Interest Paid Direct</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n">
-        <v>-22000</v>
-      </c>
+          <t>Net Income From Continuing Operations</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>-247826000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>-155407000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>384611000</v>
+      </c>
+      <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n">
-        <v>-58000</v>
+        <v>-16144000</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>-17000</v>
-      </c>
+        <v>-21888000</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Classesof Cash Payments</t>
+          <t>Cash Flowsfromusedin Operating Activities Direct</t>
         </is>
       </c>
       <c r="B61" s="3" t="n"/>
       <c r="C61" s="3" t="n"/>
       <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n">
-        <v>-56905000</v>
-      </c>
+      <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n">
-        <v>-65963000</v>
+        <v>-48012000</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-61226000</v>
+        <v>-59803000</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>-53391000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Other Cash Paymentsfrom Operating Activities</t>
+          <t>Interest Received Direct</t>
         </is>
       </c>
       <c r="B62" s="3" t="n"/>
       <c r="C62" s="3" t="n"/>
       <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
+      <c r="F62" s="3" t="n">
+        <v>2381000</v>
+      </c>
       <c r="G62" s="3" t="n">
-        <v>-61226000</v>
+        <v>992000</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>3637000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Paymentsto Suppliersfor Goodsand Services</t>
+          <t>Interest Paid Direct</t>
         </is>
       </c>
       <c r="B63" s="3" t="n"/>
       <c r="C63" s="3" t="n"/>
       <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n">
-        <v>-56905000</v>
-      </c>
+      <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n">
-        <v>-65963000</v>
+        <v>-22000</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-61226000</v>
+        <v>-58000</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>-17000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Classesof Cash Receiptsfrom Operating Activities</t>
+          <t>Classesof Cash Payments</t>
         </is>
       </c>
       <c r="B64" s="3" t="n"/>
       <c r="C64" s="3" t="n"/>
       <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n">
-        <v>6534000</v>
-      </c>
+      <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n">
-        <v>5226000</v>
+        <v>-56905000</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>4215000</v>
+        <v>-65963000</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>-61226000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Other Cash Receiptsfrom Operating Activities</t>
+          <t>Other Cash Paymentsfrom Operating Activities</t>
         </is>
       </c>
       <c r="B65" s="3" t="n"/>
       <c r="C65" s="3" t="n"/>
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n">
-        <v>1699000</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>541000</v>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n">
+        <v>-61226000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Receiptsfrom Customers</t>
+          <t>Paymentsto Suppliersfor Goodsand Services</t>
         </is>
       </c>
       <c r="B66" s="3" t="n"/>
       <c r="C66" s="3" t="n"/>
       <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n">
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n">
+        <v>-56905000</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>-65963000</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>-61226000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Classesof Cash Receiptsfrom Operating Activities</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n">
+        <v>6534000</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>5226000</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>4215000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Cash Receiptsfrom Operating Activities</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n">
+        <v>1699000</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>541000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Receiptsfrom Customers</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n">
         <v>8774000</v>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="G69" s="3" t="n">
         <v>3527000</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="H69" s="3" t="n">
         <v>3674000</v>
       </c>
     </row>
@@ -7767,7 +10560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7795,12 +10588,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>GAAP (statement) ~54% vs yfinance info.grossMargins 68% — info is a non-GAAP basis; FY Summary uses GAAP</t>
         </is>
       </c>
     </row>
